--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Raf4587ced6854f5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R7b4aa2c5842d457d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
         <x:v>发布路径关系</x:v>
       </x:c>
       <x:c r="B14" s="21" t="str">
-        <x:v>tenant_release_matrix.csv按tenant_id与flag_key唯一定位配置，config_path从reference.zip根目录书写，摘要中的config_files与矩阵集合一致</x:v>
+        <x:v>tenant_release_matrix.csv按tenant_id与flag_key唯一定位配置，config_path以output/configs为前缀并指向正式交付目录中的实际文件，摘要中的config_files与矩阵集合一致</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="56" customHeight="1">
@@ -474,7 +474,7 @@
         <x:v>失败收口</x:v>
       </x:c>
       <x:c r="B15" s="21" t="str">
-        <x:v>patch_queue.jsonl无法完整解析或候选源码非零退出时不发布本轮reports和configs；输入文件保持只读</x:v>
+        <x:v>patch_queue.jsonl无法完整解析或发布编排源码非零退出时不发布本轮reports和configs；输入文件保持只读</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R7b4aa2c5842d457d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R3f923684a6204326"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -394,7 +394,7 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="21" t="str">
-        <x:v>虚构并脱敏的功能开关基线、变更队列、租户政策、审批记录和发布合同</x:v>
+        <x:v>字段已脱敏的功能开关基线、变更队列、租户政策、审批记录和发布合同</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="62" customHeight="1">
@@ -487,18 +487,18 @@
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="14" t="str">
-        <x:v>可验证点</x:v>
+        <x:v>业务核对</x:v>
       </x:c>
       <x:c r="B17" s="21" t="str">
-        <x:v>Node.js进程与版本；五份业务输入读取；语义版本数值比较；JSON Patch原子执行；租户局部失败；矩阵路径；摘要计数与原因分布</x:v>
+        <x:v>核对五份业务输入、语义版本数值比较、JSON Patch原子执行、租户局部失败、矩阵路径，以及摘要计数与原因分布</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="14" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B18" s="21" t="str">
-        <x:v>函数拆分、变量命名、源码注释、JSON键序与缩进、CSV普通行序、LF或CRLF差异以及不改变规定业务结果的附加工程文件</x:v>
+        <x:v>输入配置、补丁队列和发布规则保持只读，不连接外部配置平台或版本服务，源码、租户配置和报告只写入output目录</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
